--- a/documentation/Construccion y Evolucion/2. Reportes de problemas/PR 1.xlsx
+++ b/documentation/Construccion y Evolucion/2. Reportes de problemas/PR 1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Proyectos\TraductorBraille\documentation\Construccion y Evolucion\2. Reportes de problemas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\translator\TraductorBrailleEspanol\documentation\Construccion y Evolucion\2. Reportes de problemas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64048153-AA03-488E-807D-F7FE4A761C40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE557D2C-6C1A-4D02-9317-EB17C6FB7732}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" xr2:uid="{AAACD53E-982C-4521-B07F-7DC6290E23F5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{AAACD53E-982C-4521-B07F-7DC6290E23F5}"/>
   </bookViews>
   <sheets>
     <sheet name="PR Formato" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Reporte de Problema</t>
   </si>
@@ -61,6 +61,15 @@
   </si>
   <si>
     <t>Observaciones</t>
+  </si>
+  <si>
+    <t>Diseño inconsistente o deficiente de los elementos interactivos, donde los botones no están claramente diferenciados visualmente y carecen de etiquetas o iconografía adecuada que describa su función, lo que genera confusión en los usuarios.</t>
+  </si>
+  <si>
+    <t>Uso de colores contrastantes, bordes definidos, iconos intuitivos, y etiquetas de texto claras que indiquen la acción esperada, asegurando que los botones se perciban claramente como elementos interactivos.</t>
+  </si>
+  <si>
+    <t>Realizar pruebas de usabilidad con usuarios reales tras implementar el rediseño, para asegurar que los cambios realmente mejoren la experiencia de uso.</t>
   </si>
 </sst>
 </file>
@@ -299,7 +308,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -341,15 +350,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -367,6 +367,30 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -703,7 +727,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67F84A08-0160-4953-9528-DB07A5F993CD}">
   <dimension ref="B1:H28"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="5.5703125" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
@@ -830,20 +854,22 @@
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="3"/>
-      <c r="C18" s="24"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="25"/>
-      <c r="G18" s="26"/>
+      <c r="C18" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="30"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="31"/>
       <c r="H18" s="12"/>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="3"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="29"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="33"/>
+      <c r="E19" s="33"/>
+      <c r="F19" s="33"/>
+      <c r="G19" s="34"/>
       <c r="H19" s="12"/>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
@@ -864,20 +890,22 @@
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="3"/>
-      <c r="C22" s="24"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="25"/>
-      <c r="F22" s="25"/>
-      <c r="G22" s="26"/>
+      <c r="C22" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="23"/>
       <c r="H22" s="12"/>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" s="3"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="29"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="25"/>
+      <c r="G23" s="26"/>
       <c r="H23" s="12"/>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.25">
@@ -895,13 +923,15 @@
       <c r="G25" s="5"/>
       <c r="H25" s="12"/>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:8" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="3"/>
-      <c r="C26" s="21"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="22"/>
-      <c r="F26" s="22"/>
-      <c r="G26" s="23"/>
+      <c r="C26" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D26" s="28"/>
+      <c r="E26" s="28"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="29"/>
       <c r="H26" s="12"/>
     </row>
     <row r="27" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
